--- a/deneme/2026-10-06_kalinlik_160_100/sonuc/PM-DENEME-3ARTI1-1150x1050/yukleme/Portman_PM-DENEME-3ARTI1-1150x1050_r01_Yukleme_Listesi.xlsx
+++ b/deneme/2026-10-06_kalinlik_160_100/sonuc/PM-DENEME-3ARTI1-1150x1050/yukleme/Portman_PM-DENEME-3ARTI1-1150x1050_r01_Yukleme_Listesi.xlsx
@@ -349,7 +349,7 @@
     <t xml:space="preserve">Orta makas</t>
   </si>
   <si>
-    <t xml:space="preserve">Pano akslarında; son aralık 114 cm. P6001 gerçek listesinde tutuyor (5).</t>
+    <t xml:space="preserve">Pano akslarında (kesilen panoda aralık kısalır). P6001 gerçek listesinde tutuyor (5).</t>
   </si>
   <si>
     <t xml:space="preserve">Çatı kaplaması, tek kat panel</t>
@@ -1654,15 +1654,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1670,11 +1670,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1714,7 +1710,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1723,6 +1719,10 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2003,7 +2003,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -2017,7 +2017,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="100"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2025,12 +2025,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="355.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -2061,1032 +2061,1032 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D09")</f>
         <v>23</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D10")</f>
         <v>3</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D11")</f>
         <v>1</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D12")</f>
         <v>2</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D13")</f>
         <v>3</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D14")</f>
         <v>2</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"D15")</f>
         <v>2</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I12")</f>
         <v>3</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I13")</f>
         <v>2</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I14")</f>
         <v>11</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="8"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I15")</f>
         <v>5</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I16")</f>
         <v>3</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I17")</f>
         <v>2</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I18")</f>
         <v>2</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"I19")</f>
         <v>2</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"P01")</f>
         <v>3</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"P02")</f>
         <v>3</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"P03")</f>
         <v>2</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"K01")</f>
         <v>5</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"K03")</f>
         <v>1</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="11" t="n">
         <f aca="false">Metraj!B38</f>
         <v>3</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="n">
+      <c r="A32" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="E32" s="14" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"B02")</f>
         <v>2</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="n">
+      <c r="A33" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E33" s="14" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"B05")</f>
         <v>4</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="n">
+      <c r="A34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E34" s="14" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"B06")</f>
         <v>4</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H34" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="11" t="n">
         <f aca="false">Metraj!B34</f>
         <v>32</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="11" t="n">
         <f aca="false">Metraj!B35</f>
         <v>19</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="11" t="n">
         <f aca="false">Metraj!B36</f>
         <v>12</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="10" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="11" t="n">
         <f aca="false">Metraj!B37</f>
         <v>9</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <f aca="false">Metraj!B40</f>
         <v>2</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="10" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="11" t="n">
         <f aca="false">Metraj!B41</f>
         <v>8</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="7" t="str">
+      <c r="D42" s="6" t="str">
         <f aca="false">CONCATENATE("L ",ROUNDUP(Metraj!B46*100,0)*10)</f>
         <v>L 5900</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <f aca="false">Metraj!B45</f>
         <v>26</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <f aca="false">Metraj!B47</f>
         <v>5</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="8" t="n">
         <f aca="false">Metraj!B48</f>
         <v>10</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <f aca="false">Metraj!B49</f>
         <v>10</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" s="7" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="11" t="n">
         <f aca="false">Metraj!B51</f>
         <v>68</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="11" t="n">
         <f aca="false">Metraj!B55</f>
         <v>13</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="10" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3094,38 +3094,38 @@
       <c r="A48" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10" t="n">
+      <c r="A49" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="11" t="n">
         <f aca="false">Metraj!B54</f>
         <v>41</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="10" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3133,229 +3133,229 @@
       <c r="A50" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="n">
+      <c r="A51" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="14" t="n">
         <f aca="false">Metraj!B57</f>
         <v>7</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H51" s="14" t="s">
+      <c r="H51" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="n">
+      <c r="A52" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="15" t="n">
+      <c r="D52" s="12"/>
+      <c r="E52" s="14" t="n">
         <f aca="false">Metraj!B59</f>
         <v>56</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H52" s="14" t="s">
+      <c r="H52" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="n">
+      <c r="A53" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="E53" s="14" t="n">
         <f aca="false">Metraj!B58</f>
         <v>6</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="G53" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="13" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="n">
+      <c r="A54" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="15" t="n">
+      <c r="D54" s="12"/>
+      <c r="E54" s="14" t="n">
         <f aca="false">Metraj!B58</f>
         <v>6</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="G54" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H54" s="14" t="s">
+      <c r="H54" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="n">
+      <c r="A55" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="15" t="n">
+      <c r="D55" s="12"/>
+      <c r="E55" s="14" t="n">
         <f aca="false">Metraj!B58</f>
         <v>6</v>
       </c>
-      <c r="F55" s="13" t="s">
+      <c r="F55" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H55" s="14" t="s">
+      <c r="H55" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="n">
+      <c r="A56" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="15" t="n">
+      <c r="D56" s="12"/>
+      <c r="E56" s="14" t="n">
         <f aca="false">Metraj!B60</f>
         <v>12</v>
       </c>
-      <c r="F56" s="13" t="s">
+      <c r="F56" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="13" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="13" t="n">
+      <c r="A57" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="15" t="n">
+      <c r="D57" s="12"/>
+      <c r="E57" s="14" t="n">
         <f aca="false">Metraj!B61</f>
         <v>12</v>
       </c>
-      <c r="F57" s="13" t="s">
+      <c r="F57" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H57" s="14" t="s">
+      <c r="H57" s="13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="18" t="n">
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="17" t="n">
         <f aca="false">E8+E9+E10+E11+E12+E13+E14+E16+E17+E18+E19+E20+E21+E22+E23</f>
         <v>66</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G59" s="17"/>
-      <c r="H59" s="16" t="str">
+      <c r="G59" s="16"/>
+      <c r="H59" s="18" t="str">
         <f aca="false">IF(E59=COUNTIF(Sayım!$C$5:$C$94,"Dış pano")+COUNTIF(Sayım!$C$5:$C$94,"İç pano"),"Sayım sayfasındaki pano satırlarıyla aynı.","UYARI: Sayım sayfasıyla tutmuyor.")</f>
         <v>Sayım sayfasındaki pano satırlarıyla aynı.</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="147.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="491.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="262.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="273.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>146</v>
       </c>
@@ -3363,7 +3363,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3374,7 +3374,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:L94"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -3391,12 +3391,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>148</v>
       </c>
@@ -3440,3209 +3440,3209 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="7" t="n">
+      <c r="I5" s="7"/>
+      <c r="J5" s="6" t="n">
         <v>78.75</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H6" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="J6" s="6" t="n">
         <v>204.25</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="n">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="n">
         <v>1800</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="6" t="n">
         <v>204.25</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="6" t="n">
         <v>329.75</v>
       </c>
-      <c r="K8" s="7" t="n">
+      <c r="K8" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7" t="n">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="n">
         <v>1800</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="6" t="n">
         <v>329.75</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="8"/>
+      <c r="L9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="6" t="n">
         <v>455.25</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="K10" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>900</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8" t="s">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="6" t="n">
         <v>455.25</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="8"/>
+      <c r="L11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="7" t="n">
+      <c r="I12" s="7"/>
+      <c r="J12" s="6" t="n">
         <v>580.75</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="7" t="n">
+      <c r="I13" s="7"/>
+      <c r="J13" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7" t="n">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="n">
         <v>1800</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="8"/>
+      <c r="L15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="7" t="n">
+      <c r="I16" s="7"/>
+      <c r="J16" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>1140</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="7" t="n">
+      <c r="I17" s="7"/>
+      <c r="J17" s="6" t="n">
         <v>1077</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>1205</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="7" t="n">
+      <c r="I18" s="7"/>
+      <c r="J18" s="6" t="n">
         <v>1022.5</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="6" t="n">
         <v>321.75</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>188</v>
       </c>
       <c r="F19" s="19" t="n">
         <v>512.5</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7" t="n">
+      <c r="I19" s="7"/>
+      <c r="J19" s="6" t="n">
         <v>1108.38</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="6" t="n">
         <v>321.75</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L19" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="7" t="n">
+      <c r="I20" s="7"/>
+      <c r="J20" s="6" t="n">
         <v>580.75</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="L20" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="L21" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>820</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="8" t="s">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L22" s="8"/>
+      <c r="L22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="7" t="n">
+      <c r="I23" s="7"/>
+      <c r="J23" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="L23" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>198</v>
       </c>
       <c r="F24" s="19" t="n">
         <v>577.5</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="7" t="n">
+      <c r="I24" s="7"/>
+      <c r="J24" s="6" t="n">
         <v>923.38</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="L24" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="7" t="n">
+      <c r="I25" s="7"/>
+      <c r="J25" s="6" t="n">
         <v>580.75</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="L25" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L26" s="8" t="s">
+      <c r="L26" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>820</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="8" t="s">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L27" s="8"/>
+      <c r="L27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>205</v>
       </c>
       <c r="F28" s="19" t="n">
         <v>627.5</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="7" t="n">
+      <c r="I28" s="7"/>
+      <c r="J28" s="6" t="n">
         <v>800.38</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L28" s="8" t="s">
+      <c r="L28" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="6" t="n">
         <v>894.5</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L29" s="8" t="s">
+      <c r="L29" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>820</v>
       </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="8" t="s">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="6" t="n">
         <v>894.5</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="K30" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L30" s="8"/>
+      <c r="L30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="7" t="n">
+      <c r="I31" s="7"/>
+      <c r="J31" s="6" t="n">
         <v>1020</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="K31" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L31" s="8" t="s">
+      <c r="L31" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="6" t="s">
         <v>211</v>
       </c>
       <c r="F32" s="19" t="n">
         <v>512.5</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="7" t="n">
+      <c r="I32" s="7"/>
+      <c r="J32" s="6" t="n">
         <v>1108.38</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L32" s="8" t="s">
+      <c r="L32" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="7" t="n">
+      <c r="I33" s="7"/>
+      <c r="J33" s="6" t="n">
         <v>78.75</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L33" s="8" t="s">
+      <c r="L33" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J34" s="7" t="n">
+      <c r="J34" s="6" t="n">
         <v>204.25</v>
       </c>
-      <c r="K34" s="7" t="n">
+      <c r="K34" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L34" s="8" t="s">
+      <c r="L34" s="7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7" t="n">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="6" t="n">
         <v>204.25</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="K35" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L35" s="8"/>
+      <c r="L35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="7" t="n">
+      <c r="I36" s="7"/>
+      <c r="J36" s="6" t="n">
         <v>329.75</v>
       </c>
-      <c r="K36" s="7" t="n">
+      <c r="K36" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L36" s="8" t="s">
+      <c r="L36" s="7" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="7" t="n">
+      <c r="I37" s="7"/>
+      <c r="J37" s="6" t="n">
         <v>455.25</v>
       </c>
-      <c r="K37" s="7" t="n">
+      <c r="K37" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L37" s="8" t="s">
+      <c r="L37" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="7" t="n">
+      <c r="I38" s="7"/>
+      <c r="J38" s="6" t="n">
         <v>580.75</v>
       </c>
-      <c r="K38" s="7" t="n">
+      <c r="K38" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L38" s="8" t="s">
+      <c r="L38" s="7" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J39" s="7" t="n">
+      <c r="J39" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L39" s="8" t="s">
+      <c r="L39" s="7" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7" t="n">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J40" s="6" t="n">
         <v>706.25</v>
       </c>
-      <c r="K40" s="7" t="n">
+      <c r="K40" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L40" s="8"/>
+      <c r="L40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I41" s="8"/>
-      <c r="J41" s="7" t="n">
+      <c r="I41" s="7"/>
+      <c r="J41" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K41" s="7" t="n">
+      <c r="K41" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L41" s="8" t="s">
+      <c r="L41" s="7" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H42" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J42" s="7" t="n">
+      <c r="J42" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K42" s="7" t="n">
+      <c r="K42" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L42" s="8" t="s">
+      <c r="L42" s="7" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7" t="n">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="I43" s="8" t="s">
+      <c r="I43" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J43" s="7" t="n">
+      <c r="J43" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K43" s="7" t="n">
+      <c r="K43" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L43" s="8"/>
+      <c r="L43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="6" t="n">
         <v>1140</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="7" t="n">
+      <c r="I44" s="7"/>
+      <c r="J44" s="6" t="n">
         <v>1077</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="K44" s="6" t="n">
         <v>1042</v>
       </c>
-      <c r="L44" s="8" t="s">
+      <c r="L44" s="7" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="7" t="n">
+      <c r="I45" s="7"/>
+      <c r="J45" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" s="6" t="n">
         <v>70.75</v>
       </c>
-      <c r="L45" s="8" t="s">
+      <c r="L45" s="7" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="7" t="n">
+      <c r="I46" s="7"/>
+      <c r="J46" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K46" s="7" t="n">
+      <c r="K46" s="6" t="n">
         <v>196.25</v>
       </c>
-      <c r="L46" s="8" t="s">
+      <c r="L46" s="7" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="7" t="n">
+      <c r="I47" s="7"/>
+      <c r="J47" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="K47" s="6" t="n">
         <v>321.75</v>
       </c>
-      <c r="L47" s="8" t="s">
+      <c r="L47" s="7" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H48" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="7" t="n">
+      <c r="I48" s="7"/>
+      <c r="J48" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K48" s="7" t="n">
+      <c r="K48" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L48" s="8" t="s">
+      <c r="L48" s="7" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H49" s="7" t="n">
+      <c r="H49" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="7" t="n">
+      <c r="I49" s="7"/>
+      <c r="J49" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K49" s="7" t="n">
+      <c r="K49" s="6" t="n">
         <v>572.75</v>
       </c>
-      <c r="L49" s="8" t="s">
+      <c r="L49" s="7" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H50" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I50" s="8"/>
-      <c r="J50" s="7" t="n">
+      <c r="I50" s="7"/>
+      <c r="J50" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K50" s="7" t="n">
+      <c r="K50" s="6" t="n">
         <v>698.25</v>
       </c>
-      <c r="L50" s="8" t="s">
+      <c r="L50" s="7" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H51" s="7" t="n">
+      <c r="H51" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I51" s="8"/>
-      <c r="J51" s="7" t="n">
+      <c r="I51" s="7"/>
+      <c r="J51" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K51" s="7" t="n">
+      <c r="K51" s="6" t="n">
         <v>823.75</v>
       </c>
-      <c r="L51" s="8" t="s">
+      <c r="L51" s="7" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F52" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H52" s="7" t="n">
+      <c r="H52" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I52" s="8"/>
-      <c r="J52" s="7" t="n">
+      <c r="I52" s="7"/>
+      <c r="J52" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K52" s="7" t="n">
+      <c r="K52" s="6" t="n">
         <v>949.25</v>
       </c>
-      <c r="L52" s="8" t="s">
+      <c r="L52" s="7" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H53" s="7" t="n">
+      <c r="H53" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I53" s="8"/>
-      <c r="J53" s="7" t="n">
+      <c r="I53" s="7"/>
+      <c r="J53" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K53" s="7" t="n">
+      <c r="K53" s="6" t="n">
         <v>1027</v>
       </c>
-      <c r="L53" s="8" t="s">
+      <c r="L53" s="7" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F54" s="6" t="n">
         <v>1175</v>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H54" s="7" t="n">
+      <c r="H54" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="7" t="n">
+      <c r="I54" s="7"/>
+      <c r="J54" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K54" s="7" t="n">
+      <c r="K54" s="6" t="n">
         <v>74.75</v>
       </c>
-      <c r="L54" s="8" t="s">
+      <c r="L54" s="7" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F55" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H55" s="7" t="n">
+      <c r="H55" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="7" t="n">
+      <c r="I55" s="7"/>
+      <c r="J55" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K55" s="7" t="n">
+      <c r="K55" s="6" t="n">
         <v>196.25</v>
       </c>
-      <c r="L55" s="8" t="s">
+      <c r="L55" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F56" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H56" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I56" s="8"/>
-      <c r="J56" s="7" t="n">
+      <c r="I56" s="7"/>
+      <c r="J56" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K56" s="7" t="n">
+      <c r="K56" s="6" t="n">
         <v>321.75</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="L56" s="7" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="6" t="s">
         <v>259</v>
       </c>
       <c r="F57" s="19" t="n">
         <v>577.5</v>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H57" s="7" t="n">
+      <c r="H57" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I57" s="8"/>
-      <c r="J57" s="7" t="n">
+      <c r="I57" s="7"/>
+      <c r="J57" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K57" s="7" t="n">
+      <c r="K57" s="6" t="n">
         <v>413.38</v>
       </c>
-      <c r="L57" s="8" t="s">
+      <c r="L57" s="7" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F58" s="6" t="n">
         <v>1205</v>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="H58" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="7" t="n">
+      <c r="I58" s="7"/>
+      <c r="J58" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K58" s="7" t="n">
+      <c r="K58" s="6" t="n">
         <v>700.75</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" s="7" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H59" s="7" t="n">
+      <c r="H59" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="7" t="n">
+      <c r="I59" s="7"/>
+      <c r="J59" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K59" s="7" t="n">
+      <c r="K59" s="6" t="n">
         <v>823.75</v>
       </c>
-      <c r="L59" s="8" t="s">
+      <c r="L59" s="7" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F60" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H60" s="7" t="n">
+      <c r="H60" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I60" s="8"/>
-      <c r="J60" s="7" t="n">
+      <c r="I60" s="7"/>
+      <c r="J60" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K60" s="7" t="n">
+      <c r="K60" s="6" t="n">
         <v>949.25</v>
       </c>
-      <c r="L60" s="8" t="s">
+      <c r="L60" s="7" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F61" s="7" t="n">
+      <c r="F61" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H61" s="7" t="n">
+      <c r="H61" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I61" s="8"/>
-      <c r="J61" s="7" t="n">
+      <c r="I61" s="7"/>
+      <c r="J61" s="6" t="n">
         <v>518</v>
       </c>
-      <c r="K61" s="7" t="n">
+      <c r="K61" s="6" t="n">
         <v>1023</v>
       </c>
-      <c r="L61" s="8" t="s">
+      <c r="L61" s="7" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="6" t="n">
         <v>1205</v>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="H62" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I62" s="8"/>
-      <c r="J62" s="7" t="n">
+      <c r="I62" s="7"/>
+      <c r="J62" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K62" s="7" t="n">
+      <c r="K62" s="6" t="n">
         <v>700.75</v>
       </c>
-      <c r="L62" s="8" t="s">
+      <c r="L62" s="7" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="H63" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I63" s="8"/>
-      <c r="J63" s="7" t="n">
+      <c r="I63" s="7"/>
+      <c r="J63" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="K63" s="6" t="n">
         <v>823.75</v>
       </c>
-      <c r="L63" s="8" t="s">
+      <c r="L63" s="7" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F64" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H64" s="7" t="n">
+      <c r="H64" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I64" s="8"/>
-      <c r="J64" s="7" t="n">
+      <c r="I64" s="7"/>
+      <c r="J64" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K64" s="7" t="n">
+      <c r="K64" s="6" t="n">
         <v>949.25</v>
       </c>
-      <c r="L64" s="8" t="s">
+      <c r="L64" s="7" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="H65" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I65" s="8"/>
-      <c r="J65" s="7" t="n">
+      <c r="I65" s="7"/>
+      <c r="J65" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K65" s="7" t="n">
+      <c r="K65" s="6" t="n">
         <v>1023</v>
       </c>
-      <c r="L65" s="8" t="s">
+      <c r="L65" s="7" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F66" s="6" t="n">
         <v>1175</v>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H66" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I66" s="8"/>
-      <c r="J66" s="7" t="n">
+      <c r="I66" s="7"/>
+      <c r="J66" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K66" s="7" t="n">
+      <c r="K66" s="6" t="n">
         <v>74.75</v>
       </c>
-      <c r="L66" s="8" t="s">
+      <c r="L66" s="7" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="F67" s="7" t="n">
+      <c r="F67" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H67" s="7" t="n">
+      <c r="H67" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I67" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J67" s="7" t="n">
+      <c r="J67" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K67" s="7" t="n">
+      <c r="K67" s="6" t="n">
         <v>196.25</v>
       </c>
-      <c r="L67" s="8" t="s">
+      <c r="L67" s="7" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F68" s="6" t="n">
         <v>820</v>
       </c>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="8" t="s">
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J68" s="7" t="n">
+      <c r="J68" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K68" s="7" t="n">
+      <c r="K68" s="6" t="n">
         <v>196.25</v>
       </c>
-      <c r="L68" s="8"/>
+      <c r="L68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="6" t="s">
         <v>284</v>
       </c>
       <c r="F69" s="19" t="n">
         <v>627.5</v>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H69" s="7" t="n">
+      <c r="H69" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I69" s="8"/>
-      <c r="J69" s="7" t="n">
+      <c r="I69" s="7"/>
+      <c r="J69" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="K69" s="6" t="n">
         <v>290.38</v>
       </c>
-      <c r="L69" s="8" t="s">
+      <c r="L69" s="7" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F70" s="7" t="n">
+      <c r="F70" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H70" s="7" t="n">
+      <c r="H70" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I70" s="8"/>
-      <c r="J70" s="7" t="n">
+      <c r="I70" s="7"/>
+      <c r="J70" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K70" s="7" t="n">
+      <c r="K70" s="6" t="n">
         <v>384.5</v>
       </c>
-      <c r="L70" s="8" t="s">
+      <c r="L70" s="7" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F71" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="H71" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I71" s="8" t="s">
+      <c r="I71" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J71" s="7" t="n">
+      <c r="J71" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="K71" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="L71" s="8" t="s">
+      <c r="L71" s="7" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="F72" s="6" t="n">
         <v>820</v>
       </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="8" t="s">
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="J72" s="7" t="n">
+      <c r="J72" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K72" s="7" t="n">
+      <c r="K72" s="6" t="n">
         <v>510</v>
       </c>
-      <c r="L72" s="8"/>
+      <c r="L72" s="7"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="6" t="s">
         <v>290</v>
       </c>
       <c r="F73" s="19" t="n">
         <v>577.5</v>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H73" s="7" t="n">
+      <c r="H73" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I73" s="8"/>
-      <c r="J73" s="7" t="n">
+      <c r="I73" s="7"/>
+      <c r="J73" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K73" s="7" t="n">
+      <c r="K73" s="6" t="n">
         <v>601.62</v>
       </c>
-      <c r="L73" s="8" t="s">
+      <c r="L73" s="7" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F74" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H74" s="7" t="n">
+      <c r="H74" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I74" s="8"/>
-      <c r="J74" s="7" t="n">
+      <c r="I74" s="7"/>
+      <c r="J74" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K74" s="7" t="n">
+      <c r="K74" s="6" t="n">
         <v>70.75</v>
       </c>
-      <c r="L74" s="8" t="s">
+      <c r="L74" s="7" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F75" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="G75" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H75" s="7" t="n">
+      <c r="H75" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I75" s="8" t="s">
+      <c r="I75" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="J75" s="7" t="n">
+      <c r="J75" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K75" s="7" t="n">
+      <c r="K75" s="6" t="n">
         <v>196.25</v>
       </c>
-      <c r="L75" s="8" t="s">
+      <c r="L75" s="7" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F76" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7" t="n">
+      <c r="G76" s="6"/>
+      <c r="H76" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="I76" s="8" t="s">
+      <c r="I76" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="J76" s="7" t="n">
+      <c r="J76" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K76" s="7" t="n">
+      <c r="K76" s="6" t="n">
         <v>196.25</v>
       </c>
-      <c r="L76" s="8"/>
+      <c r="L76" s="7"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F77" s="7" t="n">
+      <c r="F77" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="G77" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H77" s="7" t="n">
+      <c r="H77" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I77" s="8"/>
-      <c r="J77" s="7" t="n">
+      <c r="I77" s="7"/>
+      <c r="J77" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K77" s="7" t="n">
+      <c r="K77" s="6" t="n">
         <v>321.75</v>
       </c>
-      <c r="L77" s="8" t="s">
+      <c r="L77" s="7" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="D78" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F78" s="7" t="n">
+      <c r="F78" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="G78" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H78" s="7" t="n">
+      <c r="H78" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I78" s="8"/>
-      <c r="J78" s="7" t="n">
+      <c r="I78" s="7"/>
+      <c r="J78" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K78" s="7" t="n">
+      <c r="K78" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L78" s="8" t="s">
+      <c r="L78" s="7" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F79" s="7" t="n">
+      <c r="F79" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="G79" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H79" s="7" t="n">
+      <c r="H79" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I79" s="8" t="s">
+      <c r="I79" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="J79" s="7" t="n">
+      <c r="J79" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K79" s="7" t="n">
+      <c r="K79" s="6" t="n">
         <v>572.75</v>
       </c>
-      <c r="L79" s="8" t="s">
+      <c r="L79" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F80" s="7" t="n">
+      <c r="F80" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7" t="n">
+      <c r="G80" s="6"/>
+      <c r="H80" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="I80" s="8" t="s">
+      <c r="I80" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="J80" s="7" t="n">
+      <c r="J80" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K80" s="7" t="n">
+      <c r="K80" s="6" t="n">
         <v>572.75</v>
       </c>
-      <c r="L80" s="8"/>
+      <c r="L80" s="7"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="D81" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="F81" s="7" t="n">
+      <c r="F81" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G81" s="7" t="n">
+      <c r="G81" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H81" s="7" t="n">
+      <c r="H81" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I81" s="8"/>
-      <c r="J81" s="7" t="n">
+      <c r="I81" s="7"/>
+      <c r="J81" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K81" s="7" t="n">
+      <c r="K81" s="6" t="n">
         <v>698.25</v>
       </c>
-      <c r="L81" s="8" t="s">
+      <c r="L81" s="7" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="F82" s="7" t="n">
+      <c r="F82" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G82" s="7" t="n">
+      <c r="G82" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H82" s="7" t="n">
+      <c r="H82" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I82" s="8"/>
-      <c r="J82" s="7" t="n">
+      <c r="I82" s="7"/>
+      <c r="J82" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K82" s="7" t="n">
+      <c r="K82" s="6" t="n">
         <v>823.75</v>
       </c>
-      <c r="L82" s="8" t="s">
+      <c r="L82" s="7" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D83" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I83" s="8"/>
-      <c r="J83" s="7" t="n">
+      <c r="I83" s="7"/>
+      <c r="J83" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K83" s="7" t="n">
+      <c r="K83" s="6" t="n">
         <v>949.25</v>
       </c>
-      <c r="L83" s="8" t="s">
+      <c r="L83" s="7" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D84" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F84" s="7" t="n">
+      <c r="F84" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="H84" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I84" s="8"/>
-      <c r="J84" s="7" t="n">
+      <c r="I84" s="7"/>
+      <c r="J84" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K84" s="7" t="n">
+      <c r="K84" s="6" t="n">
         <v>1027</v>
       </c>
-      <c r="L84" s="8" t="s">
+      <c r="L84" s="7" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="s">
+      <c r="A85" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="D85" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="H85" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I85" s="8"/>
-      <c r="J85" s="7" t="n">
+      <c r="I85" s="7"/>
+      <c r="J85" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K85" s="7" t="n">
+      <c r="K85" s="6" t="n">
         <v>1046</v>
       </c>
-      <c r="L85" s="8"/>
+      <c r="L85" s="7"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="s">
+      <c r="A86" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="F86" s="7" t="n">
+      <c r="F86" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="G86" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="H86" s="7" t="n">
+      <c r="H86" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I86" s="8"/>
-      <c r="J86" s="7" t="n">
+      <c r="I86" s="7"/>
+      <c r="J86" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K86" s="7" t="n">
+      <c r="K86" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="L86" s="8"/>
+      <c r="L86" s="7"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F87" s="7" t="n">
+      <c r="F87" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="G87" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="H87" s="7" t="n">
+      <c r="H87" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I87" s="8"/>
-      <c r="J87" s="7" t="n">
+      <c r="I87" s="7"/>
+      <c r="J87" s="6" t="n">
         <v>515.5</v>
       </c>
-      <c r="K87" s="7" t="n">
+      <c r="K87" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L87" s="8"/>
+      <c r="L87" s="7"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="D88" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F88" s="7" t="n">
+      <c r="F88" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="G88" s="7" t="n">
+      <c r="G88" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="H88" s="7" t="n">
+      <c r="H88" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I88" s="8"/>
-      <c r="J88" s="7" t="n">
+      <c r="I88" s="7"/>
+      <c r="J88" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K88" s="7" t="n">
+      <c r="K88" s="6" t="n">
         <v>1046</v>
       </c>
-      <c r="L88" s="8"/>
+      <c r="L88" s="7"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="F89" s="7" t="n">
+      <c r="F89" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G89" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="H89" s="7" t="n">
+      <c r="H89" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I89" s="8"/>
-      <c r="J89" s="7" t="n">
+      <c r="I89" s="7"/>
+      <c r="J89" s="6" t="n">
         <v>1142</v>
       </c>
-      <c r="K89" s="7" t="n">
+      <c r="K89" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="L89" s="8"/>
+      <c r="L89" s="7"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="D90" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="F90" s="7" t="n">
+      <c r="F90" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="G90" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="H90" s="7" t="n">
+      <c r="H90" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I90" s="8"/>
-      <c r="J90" s="7" t="n">
+      <c r="I90" s="7"/>
+      <c r="J90" s="6" t="n">
         <v>515.5</v>
       </c>
-      <c r="K90" s="7" t="n">
+      <c r="K90" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L90" s="8"/>
+      <c r="L90" s="7"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="F91" s="7" t="n">
+      <c r="F91" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7" t="n">
+      <c r="G91" s="6"/>
+      <c r="H91" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I91" s="8"/>
-      <c r="J91" s="7" t="n">
+      <c r="I91" s="7"/>
+      <c r="J91" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K91" s="7" t="n">
+      <c r="K91" s="6" t="n">
         <v>321.75</v>
       </c>
-      <c r="L91" s="8"/>
+      <c r="L91" s="7"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="D92" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F92" s="7" t="n">
+      <c r="F92" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7" t="n">
+      <c r="G92" s="6"/>
+      <c r="H92" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I92" s="8"/>
-      <c r="J92" s="7" t="n">
+      <c r="I92" s="7"/>
+      <c r="J92" s="6" t="n">
         <v>831.75</v>
       </c>
-      <c r="K92" s="7" t="n">
+      <c r="K92" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L92" s="8"/>
+      <c r="L92" s="7"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F93" s="7" t="n">
+      <c r="F93" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7" t="n">
+      <c r="G93" s="6"/>
+      <c r="H93" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I93" s="8"/>
-      <c r="J93" s="7" t="n">
+      <c r="I93" s="7"/>
+      <c r="J93" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K93" s="7" t="n">
+      <c r="K93" s="6" t="n">
         <v>447.25</v>
       </c>
-      <c r="L93" s="8"/>
+      <c r="L93" s="7"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="F94" s="7" t="n">
+      <c r="F94" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7" t="n">
+      <c r="G94" s="6"/>
+      <c r="H94" s="6" t="n">
         <v>2800</v>
       </c>
-      <c r="I94" s="8"/>
-      <c r="J94" s="7" t="n">
+      <c r="I94" s="7"/>
+      <c r="J94" s="6" t="n">
         <v>957.25</v>
       </c>
-      <c r="K94" s="7" t="n">
+      <c r="K94" s="6" t="n">
         <v>635.5</v>
       </c>
-      <c r="L94" s="8"/>
+      <c r="L94" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6653,7 +6653,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -6670,7 +6670,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>327</v>
       </c>
@@ -6699,14 +6699,14 @@
       <c r="A5" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>335</v>
       </c>
       <c r="B6" s="20" t="n">
@@ -6715,14 +6715,14 @@
       <c r="C6" s="20" t="n">
         <v>773</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>337</v>
       </c>
       <c r="B7" s="20" t="n">
@@ -6731,14 +6731,14 @@
       <c r="C7" s="20" t="n">
         <v>763</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>339</v>
       </c>
       <c r="B8" s="20" t="n">
@@ -6747,14 +6747,14 @@
       <c r="C8" s="20" t="n">
         <v>773</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>341</v>
       </c>
       <c r="B9" s="20" t="n">
@@ -6763,14 +6763,14 @@
       <c r="C9" s="20" t="n">
         <v>763</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>343</v>
       </c>
       <c r="B10" s="20" t="n">
@@ -6779,14 +6779,14 @@
       <c r="C10" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>345</v>
       </c>
       <c r="B11" s="21" t="n">
@@ -6795,9 +6795,9 @@
       <c r="C11" s="21" t="n">
         <v>0.33</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6805,31 +6805,31 @@
       <c r="A12" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="6" t="n">
         <f aca="false">COUNTIF(Sayım!$C$5:$C$94,"Dış pano")</f>
         <v>36</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>350</v>
       </c>
       <c r="B14" s="20" t="n">
@@ -6838,31 +6838,31 @@
       <c r="C14" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="6" t="n">
         <f aca="false">COUNTIF(Sayım!$C$5:$C$94,"İç pano")</f>
         <v>30</v>
       </c>
       <c r="C15" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>353</v>
       </c>
       <c r="B16" s="20" t="n">
@@ -6871,31 +6871,31 @@
       <c r="C16" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="6" t="n">
         <f aca="false">COUNTIFS(Sayım!$C$5:$C$94,"Bağlantı",Sayım!$D$5:$D$94,"İç duvar T birleşimi")</f>
         <v>4</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>356</v>
       </c>
       <c r="B18" s="22" t="n">
@@ -6905,14 +6905,14 @@
       <c r="C18" s="23" t="n">
         <v>30.02</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>357</v>
       </c>
       <c r="B19" s="22" t="n">
@@ -6922,14 +6922,14 @@
       <c r="C19" s="23" t="n">
         <v>11.155</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>358</v>
       </c>
       <c r="B20" s="20" t="n">
@@ -6938,26 +6938,26 @@
       <c r="C20" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="6" t="n">
         <f aca="false">COUNTIF(Sayım!$A$5:$A$94,"P02")</f>
         <v>3</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6965,14 +6965,14 @@
       <c r="A22" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>362</v>
       </c>
       <c r="B23" s="23" t="n">
@@ -6981,14 +6981,14 @@
       <c r="C23" s="23" t="n">
         <v>3.75</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>364</v>
       </c>
       <c r="B24" s="23" t="n">
@@ -6997,14 +6997,14 @@
       <c r="C24" s="23" t="n">
         <v>0.87</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8" t="s">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>366</v>
       </c>
       <c r="B25" s="23" t="n">
@@ -7013,14 +7013,14 @@
       <c r="C25" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>368</v>
       </c>
       <c r="B26" s="23" t="n">
@@ -7029,14 +7029,14 @@
       <c r="C26" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8" t="s">
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>370</v>
       </c>
       <c r="B27" s="23" t="n">
@@ -7045,14 +7045,14 @@
       <c r="C27" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8" t="s">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>372</v>
       </c>
       <c r="B28" s="23" t="n">
@@ -7061,14 +7061,14 @@
       <c r="C28" s="23" t="n">
         <v>3.75</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8" t="s">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>374</v>
       </c>
       <c r="B29" s="21" t="n">
@@ -7077,14 +7077,14 @@
       <c r="C29" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8" t="s">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>376</v>
       </c>
       <c r="B30" s="23" t="n">
@@ -7093,14 +7093,14 @@
       <c r="C30" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8" t="s">
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>378</v>
       </c>
       <c r="B31" s="23" t="n">
@@ -7109,14 +7109,14 @@
       <c r="C31" s="23" t="n">
         <v>9.6</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8" t="s">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>380</v>
       </c>
       <c r="B32" s="23" t="n">
@@ -7125,9 +7125,9 @@
       <c r="C32" s="23" t="n">
         <v>3.8</v>
       </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8" t="s">
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7" t="s">
         <v>381</v>
       </c>
     </row>
@@ -7135,21 +7135,21 @@
       <c r="A33" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="8" t="n">
         <f aca="false">B13-B14</f>
         <v>32</v>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="8" t="n">
         <f aca="false">C13-C14</f>
         <v>19</v>
       </c>
@@ -7160,19 +7160,19 @@
         <f aca="false">IF(C34=D34,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="7" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="8" t="n">
         <f aca="false">B15-B16-B17</f>
         <v>19</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="8" t="n">
         <f aca="false">C15-C16-C17</f>
         <v>5</v>
       </c>
@@ -7183,19 +7183,19 @@
         <f aca="false">IF(C35=D35,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="7" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="8" t="n">
         <f aca="false">ROUNDUP(B18/B23,0)</f>
         <v>12</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="8" t="n">
         <f aca="false">ROUNDUP(C18/C23,0)</f>
         <v>9</v>
       </c>
@@ -7206,19 +7206,19 @@
         <f aca="false">IF(C36=D36,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="7" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="8" t="n">
         <f aca="false">ROUNDUP(B19/B23,0)</f>
         <v>9</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="8" t="n">
         <f aca="false">ROUNDUP(C19/C23,0)</f>
         <v>3</v>
       </c>
@@ -7229,19 +7229,19 @@
         <f aca="false">IF(C37=D37,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="7" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="8" t="n">
         <f aca="false">B21</f>
         <v>3</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="8" t="n">
         <f aca="false">C21</f>
         <v>2</v>
       </c>
@@ -7252,7 +7252,7 @@
         <f aca="false">IF(C38=D38,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="7" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7260,21 +7260,21 @@
       <c r="A39" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="8" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="8" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
@@ -7285,19 +7285,19 @@
         <f aca="false">IF(C40=D40,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="7" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" s="8" t="n">
         <f aca="false">B20-2</f>
         <v>8</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="8" t="n">
         <f aca="false">C20-2</f>
         <v>5</v>
       </c>
@@ -7308,12 +7308,12 @@
         <f aca="false">IF(C41=D41,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="7" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>395</v>
       </c>
       <c r="B42" s="25" t="n">
@@ -7324,16 +7324,16 @@
         <f aca="false">(C8/2+C10)/100*SQRT(1+C11^2)</f>
         <v>4.38592496544344</v>
       </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="8" t="s">
+      <c r="D42" s="6"/>
+      <c r="E42" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="7" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>397</v>
       </c>
       <c r="B43" s="22" t="n">
@@ -7344,16 +7344,16 @@
         <f aca="false">(C9+2*C10)/100</f>
         <v>8.23</v>
       </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="8" t="s">
+      <c r="D43" s="6"/>
+      <c r="E43" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>399</v>
       </c>
       <c r="B44" s="22" t="n">
@@ -7364,23 +7364,23 @@
         <f aca="false">2*C42*C43</f>
         <v>72.192324931199</v>
       </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="8" t="s">
+      <c r="D44" s="6"/>
+      <c r="E44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="7" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="8" t="n">
         <f aca="false">2*ROUNDUP(B43/B24,0)</f>
         <v>26</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="8" t="n">
         <f aca="false">2*ROUNDUP(C43/C24,0)</f>
         <v>20</v>
       </c>
@@ -7391,12 +7391,12 @@
         <f aca="false">IF(C45=D45,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="7" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>403</v>
       </c>
       <c r="B46" s="25" t="n">
@@ -7407,23 +7407,23 @@
         <f aca="false">C42+C25</f>
         <v>4.43592496544344</v>
       </c>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8" t="s">
+      <c r="D46" s="6"/>
+      <c r="E46" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="7" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B47" s="8" t="n">
         <f aca="false">ROUNDUP(B43/B26,0)</f>
         <v>5</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="8" t="n">
         <f aca="false">ROUNDUP(C43/C26,0)</f>
         <v>4</v>
       </c>
@@ -7434,19 +7434,19 @@
         <f aca="false">IF(C47=D47,"✓","✗")</f>
         <v>✗</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="7" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="8" t="n">
         <f aca="false">ROUNDUP(2*B43/B26,0)</f>
         <v>10</v>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="8" t="n">
         <f aca="false">ROUNDUP(2*C43/C26,0)</f>
         <v>7</v>
       </c>
@@ -7457,19 +7457,19 @@
         <f aca="false">IF(C48=D48,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="7" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B49" s="8" t="n">
         <f aca="false">ROUNDUP(4*B42/B26,0)</f>
         <v>10</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="8" t="n">
         <f aca="false">ROUNDUP(4*C42/C26,0)</f>
         <v>8</v>
       </c>
@@ -7480,39 +7480,39 @@
         <f aca="false">IF(C49=D49,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="7" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="8" t="n">
         <f aca="false">ROUNDDOWN(B42/B27,0)+1</f>
         <v>10</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="8" t="n">
         <f aca="false">ROUNDDOWN(C42/C27,0)+1</f>
         <v>8</v>
       </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="8" t="s">
+      <c r="D50" s="6"/>
+      <c r="E50" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="7" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" s="8" t="n">
         <f aca="false">ROUNDUP(2*B50*B43*(1+B29)/B28,0)</f>
         <v>68</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="8" t="n">
         <f aca="false">ROUNDUP(2*C50*C43*(1+C29)/C28,0)</f>
         <v>37</v>
       </c>
@@ -7523,7 +7523,7 @@
         <f aca="false">IF(C51=D51,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="7" t="s">
         <v>414</v>
       </c>
     </row>
@@ -7531,14 +7531,14 @@
       <c r="A52" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>416</v>
       </c>
       <c r="B53" s="22" t="n">
@@ -7549,23 +7549,23 @@
         <f aca="false">C6*C7/10000</f>
         <v>58.9799</v>
       </c>
-      <c r="D53" s="7"/>
-      <c r="E53" s="8" t="s">
+      <c r="D53" s="6"/>
+      <c r="E53" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F53" s="7" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="8" t="n">
         <f aca="false">ROUNDUP(B53/B30,0)</f>
         <v>41</v>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="C54" s="8" t="n">
         <f aca="false">ROUNDUP(C53/C30,0)</f>
         <v>20</v>
       </c>
@@ -7576,19 +7576,19 @@
         <f aca="false">IF(C54=D54,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="7" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B55" s="9" t="n">
+      <c r="B55" s="8" t="n">
         <f aca="false">ROUNDUP(B53/B31,0)</f>
         <v>13</v>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="8" t="n">
         <f aca="false">ROUNDUP(C53/C31,0)</f>
         <v>7</v>
       </c>
@@ -7599,124 +7599,124 @@
         <f aca="false">IF(C55=D55,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="7" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="B57" s="9" t="n">
+      <c r="B57" s="8" t="n">
         <f aca="false">ROUNDUP(2*B43/B32,0)</f>
         <v>7</v>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="8" t="n">
         <f aca="false">ROUNDUP(2*C43/C32,0)</f>
         <v>5</v>
       </c>
-      <c r="D57" s="7"/>
-      <c r="E57" s="8" t="s">
+      <c r="D57" s="6"/>
+      <c r="E57" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F57" s="7" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="B58" s="9" t="n">
+      <c r="B58" s="8" t="n">
         <f aca="false">4+IF(B43&gt;=10,2,0)</f>
         <v>6</v>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="8" t="n">
         <f aca="false">4+IF(C43&gt;=10,2,0)</f>
         <v>4</v>
       </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8" t="s">
+      <c r="D58" s="6"/>
+      <c r="E58" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="8" t="s">
+      <c r="F58" s="7" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B59" s="9" t="n">
+      <c r="B59" s="8" t="n">
         <f aca="false">B57*8</f>
         <v>56</v>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="C59" s="8" t="n">
         <f aca="false">C57*8</f>
         <v>40</v>
       </c>
-      <c r="D59" s="7"/>
-      <c r="E59" s="8" t="s">
+      <c r="D59" s="6"/>
+      <c r="E59" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F59" s="8" t="s">
+      <c r="F59" s="7" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" s="8" t="n">
         <f aca="false">B58*2</f>
         <v>12</v>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C60" s="8" t="n">
         <f aca="false">C58*2</f>
         <v>8</v>
       </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="8" t="s">
+      <c r="D60" s="6"/>
+      <c r="E60" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="7" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B61" s="9" t="n">
+      <c r="B61" s="8" t="n">
         <f aca="false">B58*2</f>
         <v>12</v>
       </c>
-      <c r="C61" s="9" t="n">
+      <c r="C61" s="8" t="n">
         <f aca="false">C58*2</f>
         <v>8</v>
       </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8" t="s">
+      <c r="D61" s="6"/>
+      <c r="E61" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="7" t="s">
         <v>430</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7727,7 +7727,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -7739,7 +7739,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="58"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>432</v>
       </c>
@@ -7762,230 +7762,230 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>485</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
